--- a/vessels/vessels_db.xlsx
+++ b/vessels/vessels_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C312"/>
+  <dimension ref="A1:C320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4479,6 +4479,110 @@
       </c>
       <c r="C312" t="n">
         <v>23820</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>CMA CGM BENJAMIN FRANKLIN</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>9706891</v>
+      </c>
+      <c r="C313" t="n">
+        <v>17859</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>CMA CGM MARCO POLO</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>9454436</v>
+      </c>
+      <c r="C314" t="n">
+        <v>16022</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>CMA CGM PANAMA</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>9839923</v>
+      </c>
+      <c r="C315" t="n">
+        <v>15128</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>COSCO SHIPPING PLANET</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>9795660</v>
+      </c>
+      <c r="C316" t="n">
+        <v>21237</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>MAERSK CINCINNATI</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>9936410</v>
+      </c>
+      <c r="C317" t="n">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>MAERSK ELBA</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>9458078</v>
+      </c>
+      <c r="C318" t="n">
+        <v>13092</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>MAERSK EMDEN</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>9456769</v>
+      </c>
+      <c r="C319" t="n">
+        <v>13092</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>MAERSK ENSENADA</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>9502958</v>
+      </c>
+      <c r="C320" t="n">
+        <v>13092</v>
       </c>
     </row>
   </sheetData>

--- a/vessels/vessels_db.xlsx
+++ b/vessels/vessels_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C320"/>
+  <dimension ref="A1:C328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4583,6 +4583,110 @@
       </c>
       <c r="C320" t="n">
         <v>13092</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>COSCO SHIPPING ARIES</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>9783497</v>
+      </c>
+      <c r="C321" t="n">
+        <v>19273</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>CSCL MARS</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>9467287</v>
+      </c>
+      <c r="C322" t="n">
+        <v>14074</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>MSC DENISSE X</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>9219795</v>
+      </c>
+      <c r="C323" t="n">
+        <v>9578</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>MSC IVANA</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>9398371</v>
+      </c>
+      <c r="C324" t="n">
+        <v>11668</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>MSC JASMINE X</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>9214903</v>
+      </c>
+      <c r="C325" t="n">
+        <v>9578</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>MSC MUMBAI VIII</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>9294991</v>
+      </c>
+      <c r="C326" t="n">
+        <v>8814</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>MSC VANDYA</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>9484467</v>
+      </c>
+      <c r="C327" t="n">
+        <v>13050</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>XIN NAN TONG</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>9262132</v>
+      </c>
+      <c r="C328" t="n">
+        <v>4051</v>
       </c>
     </row>
   </sheetData>

--- a/vessels/vessels_db.xlsx
+++ b/vessels/vessels_db.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\demo\capaStudy\vessels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A07FBEF-0C77-4E93-88C1-9C1B49898FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCDBBCB-7843-42E2-AE70-B1AFAD340F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5130" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vessels" sheetId="1" r:id="rId1"/>
@@ -40177,8 +40177,8 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.06640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.3">

--- a/vessels/vessels_db.xlsx
+++ b/vessels/vessels_db.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,56 +414,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J321"/>
+  <dimension ref="A1:J325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>vesselName</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>IMO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TEU</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>VesselName</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>vesselCode</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>group_index</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>result_ts</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
@@ -6880,6 +6868,86 @@
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>MSC CATANIA</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>9964247</v>
+      </c>
+      <c r="C322" t="n">
+        <v>15576</v>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>MSC ELEONORE</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>9954735</v>
+      </c>
+      <c r="C323" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>SEASPAN BEACON</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>9713337</v>
+      </c>
+      <c r="C324" t="n">
+        <v>10100</v>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+      <c r="J324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>YM THRONE</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>9792694</v>
+      </c>
+      <c r="C325" t="n">
+        <v>11714</v>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
+      <c r="J325" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6896,17 +6964,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>vesselName</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>IMO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TEU</t>
         </is>
